--- a/РАБОЧИЙ СТОЛ/расчеты Останкино КИ/дв 12,10,26 бррсч ост ки.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты Останкино КИ/дв 12,10,26 бррсч ост ки.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC54A750-E048-45E9-9B3C-3C7CE08672A0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{236F7C2F-69FF-4498-B04D-9F62E5A0EB56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,15 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AE$107</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -592,17 +584,23 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="10"/>
@@ -622,6 +620,8 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="8">
@@ -6034,7 +6034,7 @@
         <v>18.399999999999999</v>
       </c>
       <c r="Q48" s="5">
-        <f t="shared" ref="Q47:Q64" si="15">15*P48-O48-F48</f>
+        <f t="shared" ref="Q48:Q64" si="15">15*P48-O48-F48</f>
         <v>141</v>
       </c>
       <c r="R48" s="1">
@@ -12383,7 +12383,9 @@
       <c r="G107" s="11">
         <v>0</v>
       </c>
-      <c r="H107" s="10"/>
+      <c r="H107" s="10">
+        <v>60</v>
+      </c>
       <c r="I107" s="10" t="s">
         <v>36</v>
       </c>
